--- a/demo/configs/SkillConfig.xlsx
+++ b/demo/configs/SkillConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t>id</t>
   </si>
@@ -49,7 +49,7 @@
     <t>1001</t>
   </si>
   <si>
-    <t>开拓者·毁灭-普攻</t>
+    <t>炎锋·旅者-普通攻击</t>
   </si>
   <si>
     <t>basic</t>
@@ -67,13 +67,13 @@
     <t>20</t>
   </si>
   <si>
-    <t>对敌方单体造成等同于{Attack}100%的物理伤害</t>
+    <t>对敌方单体造成等同于{Attack}100%的火伤害</t>
   </si>
   <si>
     <t>100102</t>
   </si>
   <si>
-    <t>开拓者·毁灭-战技</t>
+    <t>炎锋·旅者-元素战技</t>
   </si>
   <si>
     <t>skill</t>
@@ -88,13 +88,13 @@
     <t>30</t>
   </si>
   <si>
-    <t>对敌方单体造成2段，每段{Attack}70%的伤害</t>
+    <t>对敌方单体造成2段，每段{Attack}70%的火伤害</t>
   </si>
   <si>
     <t>100103</t>
   </si>
   <si>
-    <t>开拓者·毁灭-终结技</t>
+    <t>炎锋·旅者-元素爆发</t>
   </si>
   <si>
     <t>ultimate</t>
@@ -109,7 +109,7 @@
     <t>0</t>
   </si>
   <si>
-    <t>对敌方全体造成{Attack}280%的伤害</t>
+    <t>对敌方全体造成{Attack}280%的火伤害</t>
   </si>
   <si>
     <t>100201</t>
@@ -118,37 +118,37 @@
     <t>1002</t>
   </si>
   <si>
-    <t>巡星·猎手-普攻</t>
+    <t>湍流·猎手-普通攻击</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>对敌方单体造成等同于{Attack}110%的物理伤害</t>
+    <t>对敌方单体造成等同于{Attack}110%的水伤害</t>
   </si>
   <si>
     <t>100202</t>
   </si>
   <si>
-    <t>巡星·猎手-战技</t>
+    <t>湍流·猎手-元素战技</t>
   </si>
   <si>
     <t>180</t>
   </si>
   <si>
-    <t>对敌方单体造成2段，每段{Attack}90%的伤害</t>
+    <t>对敌方单体造成2段，每段{Attack}90%的水伤害</t>
   </si>
   <si>
     <t>100203</t>
   </si>
   <si>
-    <t>巡星·猎手-终结技</t>
+    <t>湍流·猎手-元素爆发</t>
   </si>
   <si>
     <t>320</t>
   </si>
   <si>
-    <t>对敌方全体造成{Attack}320%的伤害</t>
+    <t>对敌方全体造成{Attack}320%的水伤害</t>
   </si>
   <si>
     <t>100301</t>
@@ -157,37 +157,37 @@
     <t>1003</t>
   </si>
   <si>
-    <t>智识·星火-普攻</t>
+    <t>惊雷·秘法-普通攻击</t>
   </si>
   <si>
     <t>90</t>
   </si>
   <si>
-    <t>对敌方单体造成等同于{Attack}90%的物理伤害</t>
+    <t>对敌方单体造成等同于{Attack}90%的雷伤害</t>
   </si>
   <si>
     <t>100302</t>
   </si>
   <si>
-    <t>智识·星火-战技</t>
+    <t>惊雷·秘法-元素战技</t>
   </si>
   <si>
     <t>160</t>
   </si>
   <si>
-    <t>对敌方单体造成2段，每段{Attack}80%的伤害</t>
+    <t>对敌方单体造成2段，每段{Attack}80%的雷伤害</t>
   </si>
   <si>
     <t>100303</t>
   </si>
   <si>
-    <t>智识·星火-终结技</t>
+    <t>惊雷·秘法-元素爆发</t>
   </si>
   <si>
     <t>350</t>
   </si>
   <si>
-    <t>对敌方全体造成{Attack}350%的伤害</t>
+    <t>对敌方全体造成{Attack}350%的雷伤害</t>
   </si>
   <si>
     <t>100401</t>
@@ -196,25 +196,28 @@
     <t>1004</t>
   </si>
   <si>
-    <t>存护·壁垒-普攻</t>
+    <t>冻土·壁垒-普通攻击</t>
+  </si>
+  <si>
+    <t>对敌方单体造成等同于{Attack}90%的冰伤害</t>
   </si>
   <si>
     <t>100402</t>
   </si>
   <si>
-    <t>存护·壁垒-战技</t>
-  </si>
-  <si>
-    <t>对敌方单体造成2段，每段{Attack}55%的伤害</t>
+    <t>冻土·壁垒-元素战技</t>
+  </si>
+  <si>
+    <t>对敌方单体造成2段，每段{Attack}55%的冰伤害</t>
   </si>
   <si>
     <t>100403</t>
   </si>
   <si>
-    <t>存护·壁垒-终结技</t>
-  </si>
-  <si>
-    <t>对敌方全体造成{Attack}180%的伤害</t>
+    <t>冻土·壁垒-元素爆发</t>
+  </si>
+  <si>
+    <t>对敌方全体造成{Attack}180%的冰伤害</t>
   </si>
   <si>
     <t>100501</t>
@@ -223,28 +226,31 @@
     <t>1005</t>
   </si>
   <si>
-    <t>丰饶·清泉-普攻</t>
+    <t>疾风·吟游-普通攻击</t>
+  </si>
+  <si>
+    <t>对敌方单体造成等同于{Attack}90%的风伤害</t>
   </si>
   <si>
     <t>100502</t>
   </si>
   <si>
-    <t>丰饶·清泉-战技</t>
-  </si>
-  <si>
-    <t>对敌方单体造成2段，每段{Attack}50%的伤害</t>
+    <t>疾风·吟游-元素战技</t>
+  </si>
+  <si>
+    <t>对敌方单体造成2段，每段{Attack}50%的风伤害</t>
   </si>
   <si>
     <t>100503</t>
   </si>
   <si>
-    <t>丰饶·清泉-终结技</t>
+    <t>疾风·吟游-元素爆发</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
-    <t>对敌方全体造成{Attack}150%的伤害</t>
+    <t>对敌方全体造成{Attack}150%的风伤害</t>
   </si>
   <si>
     <t>100601</t>
@@ -253,28 +259,31 @@
     <t>1006</t>
   </si>
   <si>
-    <t>同谐·回响-普攻</t>
+    <t>磐岩·重锋-普通攻击</t>
+  </si>
+  <si>
+    <t>对敌方单体造成等同于{Attack}90%的岩伤害</t>
   </si>
   <si>
     <t>100602</t>
   </si>
   <si>
-    <t>同谐·回响-战技</t>
+    <t>磐岩·重锋-元素战技</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
-    <t>对敌方单体造成2段，每段{Attack}60%的伤害</t>
+    <t>对敌方单体造成2段，每段{Attack}60%的岩伤害</t>
   </si>
   <si>
     <t>100603</t>
   </si>
   <si>
-    <t>同谐·回响-终结技</t>
-  </si>
-  <si>
-    <t>对敌方全体造成{Attack}160%的伤害</t>
+    <t>磐岩·重锋-元素爆发</t>
+  </si>
+  <si>
+    <t>对敌方全体造成{Attack}160%的岩伤害</t>
   </si>
 </sst>
 </file>
@@ -897,18 +906,18 @@
         <v>16</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
         <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
@@ -926,18 +935,18 @@
         <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
         <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -955,18 +964,18 @@
         <v>30</v>
       </c>
       <c r="I13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
@@ -984,18 +993,18 @@
         <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
@@ -1013,18 +1022,18 @@
         <v>23</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
@@ -1036,24 +1045,24 @@
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s">
         <v>30</v>
       </c>
       <c r="I16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
@@ -1071,18 +1080,18 @@
         <v>16</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" t="s">
         <v>80</v>
       </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
         <v>20</v>
@@ -1094,24 +1103,24 @@
         <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s">
         <v>23</v>
       </c>
       <c r="I18" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
@@ -1129,7 +1138,7 @@
         <v>30</v>
       </c>
       <c r="I19" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
